--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李坤纬_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李坤纬_脚本与截图/软件测试测试用例.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-001</t>
+          <t>TC-SL-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间等级</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>获取空间等级列表</t>
+          <t>获取等级列表_正常</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1. GET /space/list/level</t>
+          <t>GET /space/list/level</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, 含普通版/专业版/旗舰版</t>
+          <t>code=0, 3个等级</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -603,7 +603,7 @@
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-002</t>
+          <t>TC-SL-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间等级</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -626,22 +626,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>创建空间_普通版</t>
+          <t>获取等级列表_未登录</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName='我的空间' spaceLevel=0</t>
+          <t>GET /space/list/level 无Cookie</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, spaceId 存在</t>
+          <t>code=0, 不需要登录</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-003</t>
+          <t>TC-SS-001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间保存</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -675,26 +675,26 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>创建空间_名称为空</t>
+          <t>保存_正常</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName=''</t>
+          <t>POST /space/save spaceName='保存测试'</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-004</t>
+          <t>TC-SS-002</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间保存</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -728,26 +728,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>创建空间_名称超长</t>
+          <t>保存_名称为空</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName=50+'x'</t>
+          <t>spaceName=''</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -762,7 +762,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-005</t>
+          <t>TC-SA-001</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间新增</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -781,26 +781,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>创建空间_未登录</t>
+          <t>新增_正常</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add</t>
+          <t>POST /space/add spaceName='新空间' spaceLevel=0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-001</t>
+          <t>TC-SA-002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间新增</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -838,22 +838,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>添加空间成员</t>
+          <t>新增_名称超长50</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录, testuser01 有空间</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/add spaceId=1 userId=2 spaceRole='viewer'</t>
+          <t>spaceName=50+'x'</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-002</t>
+          <t>TC-SA-003</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间新增</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>查询空间成员列表</t>
+          <t>新增_未登录</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/list spaceId=1</t>
+          <t>POST /space/add</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>返回成员列表</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -921,7 +921,7 @@
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-003</t>
+          <t>TC-SG-001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间获取</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -940,26 +940,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>添加成员_重复</t>
+          <t>按id获取_正常</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>成员已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. 重复 TC-SU-001</t>
+          <t>GET /space/get?id=1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -974,7 +974,7 @@
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-004</t>
+          <t>TC-SG-002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间获取</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -993,11 +993,11 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>添加成员_未登录</t>
+          <t>按id获取_不存在</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/add</t>
+          <t>GET /space/get?id=999999</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-005</t>
+          <t>TC-SV-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间VO</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>删除空间成员</t>
+          <t>获取VO_正常</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/delete id=1</t>
+          <t>GET /space/get/vo?id=1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, isDelete=1</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-SV-002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1090,35 +1090,35 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/空间VO</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>空间分析_20并发</t>
+          <t>获取VO_未登录</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 20 线程 POST /space/analyze/usage</t>
+          <t>GET /space/get/vo?id=1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 1s, 错误率 &lt; 1%</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-SP-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1143,36 +1143,35 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间分页</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>创建空间_缺Content-Type</t>
+          <t>分页查询_正常</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1. 不设置 Content-Type
-2. POST /space/add JSON body</t>
+          <t>POST /space/list/page current=1 pageSize=10</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>返回 415 或服务端能解析</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1187,7 +1186,7 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-SP-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1197,12 +1196,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间分页</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1210,22 +1209,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>空间名称XSS</t>
+          <t>分页查询_空页</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/add spaceName='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+          <t>current=9999</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, 渲染时应被转义</t>
+          <t>code=0, []</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1240,7 +1239,7 @@
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-006</t>
+          <t>TC-LV-001</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1250,7 +1249,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间VO分页</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1259,26 +1258,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>创建_重复同名空间</t>
+          <t>VO分页_正常</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1. 重复创建相同 spaceName</t>
+          <t>POST /space/list/page/vo</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 或 code=0(允许同名)</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1293,7 +1292,7 @@
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-007</t>
+          <t>TC-LV-002</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1303,7 +1302,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间VO分页</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1312,26 +1311,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>创建_名称50字符</t>
+          <t>VO分页_未登录</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName=50+'x'</t>
+          <t>POST /space/list/page/vo</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 超长</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1346,7 +1345,7 @@
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-008</t>
+          <t>TC-SE-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1356,7 +1355,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间编辑</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1365,26 +1364,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>创建_名称含特殊字符</t>
+          <t>编辑_正常</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01是创建者</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName='my space!@#'</t>
+          <t>POST /space/edit id=1 spaceName='改名'</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1399,7 +1398,7 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-009</t>
+          <t>TC-SE-002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1409,7 +1408,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间编辑</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1418,26 +1417,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>创建_名称含中文</t>
+          <t>编辑_越权</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName='我的空间'</t>
+          <t>POST /space/edit id=别人空间</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 支持中文</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1452,7 +1451,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-010</t>
+          <t>TC-SD-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1462,7 +1461,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/空间删除</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1471,26 +1470,26 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>创建_旗舰版spaceLevel=3</t>
+          <t>删除_正常</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01是创建者</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1. spaceName='旗舰' spaceLevel=3</t>
+          <t>POST /space/delete id=1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=0, isDelete=1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1505,7 +1504,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-006</t>
+          <t>TC-SD-002</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1515,7 +1514,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间删除</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1524,26 +1523,26 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>成员_重复添加</t>
+          <t>删除_越权</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1. 重复添加同一成员</t>
+          <t>POST /space/delete id=别人空间</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1558,7 +1557,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-007</t>
+          <t>TC-SU-001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1568,7 +1567,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间更新</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1577,26 +1576,26 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>成员_添加自己</t>
+          <t>更新_正常</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01是创建者</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1. userId=当前用户自己</t>
+          <t>POST /space/update id=1 spaceName='更新'</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 不能加自己</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1611,7 +1610,7 @@
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-008</t>
+          <t>TC-SU-002</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1621,7 +1620,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/空间更新</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1630,26 +1629,26 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>成员_查询不存在的空间</t>
+          <t>更新_越权</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1. POST /spaceUser/list spaceId=999999</t>
+          <t>POST /space/update</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>返回空列表</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1664,7 +1663,7 @@
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-009</t>
+          <t>TC-MA-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1674,35 +1673,35 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/成员添加</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>成员_缺spaceId</t>
+          <t>管理员添加_正常</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1. body 无 spaceId</t>
+          <t>POST /spaceUser/add spaceId=1 userId=2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1717,7 +1716,7 @@
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-SU-010</t>
+          <t>TC-MA-002</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1727,7 +1726,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/成员添加</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1736,26 +1735,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>成员_删除已删除的成员</t>
+          <t>添加_重复</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1. 重复 delete 同一成员</t>
+          <t>重复添加</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 第二次失败</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1770,7 +1769,7 @@
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-SA-001</t>
+          <t>TC-MA-003</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1780,7 +1779,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/成员添加</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1793,22 +1792,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>空间分类分析</t>
+          <t>添加_普通用户越权</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>testuser01 有空间</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/analyze/category spaceId=1</t>
+          <t>POST /spaceUser/add</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 分类统计</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1823,7 +1822,7 @@
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-SA-002</t>
+          <t>TC-MD-001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1833,7 +1832,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/成员删除</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1846,22 +1845,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>空间标签分析</t>
+          <t>删除_正常</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>testuser01 有空间</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/analyze/tag spaceId=1</t>
+          <t>POST /spaceUser/delete id=1</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 标签统计</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1876,7 +1875,7 @@
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-SA-003</t>
+          <t>TC-MD-002</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1886,7 +1885,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>/空间分析</t>
+          <t>/成员删除</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1899,22 +1898,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>空间排行</t>
+          <t>删除_越权</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/analyze/rank</t>
+          <t>POST /spaceUser/delete</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 排行列表</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -1929,7 +1928,7 @@
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-002</t>
+          <t>TC-MG-001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1939,12 +1938,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>/空间管理</t>
+          <t>/成员查询</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -1952,22 +1951,22 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>跨用户删除空间</t>
+          <t>查询_正常</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>testuser02 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1. POST /space/delete id=testuser01的空间</t>
+          <t>POST /spaceUser/get spaceId=1 userId=2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>返回code=40300 越权失败</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1982,7 +1981,7 @@
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-MG-002</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1992,35 +1991,35 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>/空间列表</t>
+          <t>/成员查询</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>空间列表_50并发</t>
+          <t>查询_普通用户</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程 POST /space/list/page/vo</t>
+          <t>POST /spaceUser/get</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms, 错误率 &lt; 1%</t>
+          <t>code=40100或code=0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2035,7 +2034,7 @@
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-API-002</t>
+          <t>TC-ML-001</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2045,35 +2044,35 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>/空间成员</t>
+          <t>/成员列表</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>添加成员_缺userId</t>
+          <t>列表_正常</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1. body 只有 spaceId 和 spaceRole</t>
+          <t>POST /spaceUser/list spaceId=1</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, 成员列表</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2085,8 +2084,962 @@
       </c>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-ML-002</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>/成员列表</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>列表_未登录</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/list</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-ME-001</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>/成员编辑</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>编辑_正常</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/edit id=1 spaceRole='editor'</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TC-ME-002</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>/成员编辑</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>编辑_越权</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>testuser02</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/edit</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-LM-001</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/我的空间</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>我的空间列表</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/list/my</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>code=0, 我加入的空间</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TC-LM-002</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/我的空间</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>我的空间_未登录</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/list/my</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TC-AU-001</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>/空间用量分析</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>用量分析_正常</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/usage spaceId=1</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TC-AC-001</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/空间分类分析</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>分类分析_正常</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/category spaceId=1</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TC-AT-001</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/空间标签分析</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>标签分析_正常</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/tag spaceId=1</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TC-AZ-001</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/空间大小分析</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>大小分析_正常</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/size spaceId=1</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TC-AP-001</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/空间用户分析</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>用户分析_正常</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有空间</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/user spaceId=1</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TC-AR-001</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>/空间排行</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>排行_正常</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/rank</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TC-AR-002</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>/空间排行</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>排行_未登录</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>POST /space/analyze/rank</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-001</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/空间分析</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>用量分析_20并发</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>20线程 POST /space/analyze/usage</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;1s</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="80" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-002</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>/空间列表</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>空间列表_50并发</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>50线程 POST /space/list/page/vo</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;500ms</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="80" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-001</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/空间新增</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>新增_缺Content-Type</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>不设置Content-Type</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="80" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-002</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>/成员添加</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>添加_缺userId</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>无userId字段</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="80" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>/空间管理</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>空间名称XSS</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>spaceName='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>code=0, 转义</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="80" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-002</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>/成员管理</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>跨用户添加成员</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>testuser02</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>POST /spaceUser/add spaceId=别人空间</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>李坤纬</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M30"/>
+  <autoFilter ref="A1:M48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2123,23 +3076,23 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -2163,7 +3116,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李坤纬_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李坤纬_脚本与截图/软件测试测试用例.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>/space/list/level</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>/space/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/space/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/space/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/space/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/space/save</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/space/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/space/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/space/get/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>/space/list/page</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/space/list/page</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>/space/list/page/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>/space/edit</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>/space/edit</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>/space/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>/space/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>/space/update</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/list</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/list/my</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/edit</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>/spaceUser/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/usage</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/category</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/tag</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/size</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/user</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/rank</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/usage</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>/space/analyze/usage</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
